--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_8.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,485 +469,6735 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:54.889</t>
+          <t>2026-05-29 09:36:58.076</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421796748</v>
+        <v>1780022216899</v>
       </c>
       <c r="C2" t="n">
-        <v>86499</v>
+        <v>87825</v>
       </c>
       <c r="D2" t="n">
-        <v>-383.44</v>
+        <v>1407.67</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F2" t="n">
-        <v>745</v>
+        <v>679</v>
       </c>
       <c r="G2" t="n">
-        <v>110.82</v>
+        <v>279.99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L2" t="n">
+        <v>111</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.488</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:54.947</t>
+          <t>2026-05-29 09:36:58.216</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421796949</v>
+        <v>1780022217099</v>
       </c>
       <c r="C3" t="n">
-        <v>86732</v>
+        <v>86540</v>
       </c>
       <c r="D3" t="n">
-        <v>-131.27</v>
+        <v>52.28</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
-        <v>745</v>
+        <v>679</v>
       </c>
       <c r="G3" t="n">
-        <v>110.82</v>
+        <v>279.99</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1115</v>
+      </c>
+      <c r="L3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:54.949</t>
+          <t>2026-05-29 09:36:58.230</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421797150</v>
+        <v>1780022217299</v>
       </c>
       <c r="C4" t="n">
-        <v>86941</v>
+        <v>85726</v>
       </c>
       <c r="D4" t="n">
-        <v>84.29000000000001</v>
+        <v>-764.33</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" t="n">
-        <v>745</v>
+        <v>679</v>
       </c>
       <c r="G4" t="n">
-        <v>107.62</v>
+        <v>279.99</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>930</v>
+      </c>
+      <c r="L4" t="n">
+        <v>117</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:55.772</t>
+          <t>2026-05-29 09:36:58.645</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421797352</v>
+        <v>1780022217499</v>
       </c>
       <c r="C5" t="n">
-        <v>86414</v>
+        <v>84887</v>
       </c>
       <c r="D5" t="n">
-        <v>-446.92</v>
+        <v>-1565.11</v>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>745</v>
+        <v>679</v>
       </c>
       <c r="G5" t="n">
-        <v>107.62</v>
+        <v>279.99</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1145</v>
+      </c>
+      <c r="L5" t="n">
+        <v>113</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:55.772</t>
+          <t>2026-05-29 09:36:58.648</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421797553</v>
+        <v>1780022217699</v>
       </c>
       <c r="C6" t="n">
-        <v>86643</v>
+        <v>83450</v>
       </c>
       <c r="D6" t="n">
-        <v>-195.57</v>
+        <v>-2923.86</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>745</v>
+        <v>679</v>
       </c>
       <c r="G6" t="n">
-        <v>107.62</v>
+        <v>279.99</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>947</v>
+      </c>
+      <c r="L6" t="n">
+        <v>113</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.894</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:55.773</t>
+          <t>2026-05-29 09:36:59.469</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421797755</v>
+        <v>1780022217918</v>
       </c>
       <c r="C7" t="n">
-        <v>86849</v>
+        <v>84456</v>
       </c>
       <c r="D7" t="n">
-        <v>20.2</v>
+        <v>-1771.66</v>
       </c>
       <c r="E7" t="n">
         <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>766</v>
+        <v>679</v>
       </c>
       <c r="G7" t="n">
-        <v>104.82</v>
+        <v>279.99</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1550</v>
+      </c>
+      <c r="L7" t="n">
+        <v>106</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.981</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:55.774</t>
+          <t>2026-05-29 09:36:59.472</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421797956</v>
+        <v>1780022218118</v>
       </c>
       <c r="C8" t="n">
-        <v>86837</v>
+        <v>83955</v>
       </c>
       <c r="D8" t="n">
-        <v>7.19</v>
+        <v>-2184.08</v>
       </c>
       <c r="E8" t="n">
         <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>766</v>
+        <v>679</v>
       </c>
       <c r="G8" t="n">
-        <v>104.82</v>
+        <v>279.99</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1352</v>
+      </c>
+      <c r="L8" t="n">
+        <v>110</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:56.166</t>
+          <t>2026-05-29 09:37:00.363</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421798157</v>
+        <v>1780022218318</v>
       </c>
       <c r="C9" t="n">
-        <v>86780</v>
+        <v>83663</v>
       </c>
       <c r="D9" t="n">
-        <v>-50.17</v>
+        <v>-2366.88</v>
       </c>
       <c r="E9" t="n">
         <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>766</v>
+        <v>679</v>
       </c>
       <c r="G9" t="n">
-        <v>104.82</v>
+        <v>279.99</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2044</v>
+      </c>
+      <c r="L9" t="n">
+        <v>118</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.973</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:56.166</t>
+          <t>2026-05-29 09:37:00.365</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421798359</v>
+        <v>1780022218518</v>
       </c>
       <c r="C10" t="n">
-        <v>87536</v>
+        <v>83990</v>
       </c>
       <c r="D10" t="n">
-        <v>708.34</v>
+        <v>-1921.53</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="G10" t="n">
-        <v>110.62</v>
+        <v>279.99</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1846</v>
+      </c>
+      <c r="L10" t="n">
+        <v>113</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.672</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:56.694</t>
+          <t>2026-05-29 09:37:00.396</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421798560</v>
+        <v>1780022218718</v>
       </c>
       <c r="C11" t="n">
-        <v>87873</v>
+        <v>84816</v>
       </c>
       <c r="D11" t="n">
-        <v>1009.93</v>
+        <v>-999.46</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F11" t="n">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="G11" t="n">
-        <v>110.62</v>
+        <v>279.99</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1676</v>
+      </c>
+      <c r="L11" t="n">
+        <v>106</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:56.694</t>
+          <t>2026-05-29 09:37:00.397</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421798762</v>
+        <v>1780022218918</v>
       </c>
       <c r="C12" t="n">
-        <v>87383</v>
+        <v>86770</v>
       </c>
       <c r="D12" t="n">
-        <v>469.43</v>
+        <v>1004.52</v>
       </c>
       <c r="E12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="G12" t="n">
-        <v>110.62</v>
+        <v>279.99</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1478</v>
+      </c>
+      <c r="L12" t="n">
+        <v>116</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:57.403</t>
+          <t>2026-05-29 09:37:00.415</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421798963</v>
+        <v>1780022219118</v>
       </c>
       <c r="C13" t="n">
-        <v>87595</v>
+        <v>85687</v>
       </c>
       <c r="D13" t="n">
-        <v>657.96</v>
+        <v>-128.71</v>
       </c>
       <c r="E13" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="G13" t="n">
-        <v>110.62</v>
+        <v>279.99</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1296</v>
+      </c>
+      <c r="L13" t="n">
+        <v>113</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.993</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:57.404</t>
+          <t>2026-05-29 09:37:00.417</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421799165</v>
+        <v>1780022219318</v>
       </c>
       <c r="C14" t="n">
-        <v>87605</v>
+        <v>85239</v>
       </c>
       <c r="D14" t="n">
-        <v>635.0599999999999</v>
+        <v>-570.27</v>
       </c>
       <c r="E14" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F14" t="n">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="G14" t="n">
-        <v>110.62</v>
+        <v>279.99</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1098</v>
+      </c>
+      <c r="L14" t="n">
+        <v>106</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.957</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:57.405</t>
+          <t>2026-05-29 09:37:00.769</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421799366</v>
+        <v>1780022219537</v>
       </c>
       <c r="C15" t="n">
-        <v>87779</v>
+        <v>84736</v>
       </c>
       <c r="D15" t="n">
-        <v>777.3099999999999</v>
+        <v>-1044.76</v>
       </c>
       <c r="E15" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F15" t="n">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="G15" t="n">
-        <v>110.62</v>
+        <v>279.99</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L15" t="n">
+        <v>112</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.046</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:57.406</t>
+          <t>2026-05-29 09:37:00.771</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421799567</v>
+        <v>1780022219737</v>
       </c>
       <c r="C16" t="n">
-        <v>87190</v>
+        <v>85516</v>
       </c>
       <c r="D16" t="n">
-        <v>149.44</v>
+        <v>-212.52</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="G16" t="n">
-        <v>110.62</v>
+        <v>279.99</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1033</v>
+      </c>
+      <c r="L16" t="n">
+        <v>109</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.881</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:57.835</t>
+          <t>2026-05-29 09:37:00.772</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421799769</v>
+        <v>1780022219937</v>
       </c>
       <c r="C17" t="n">
-        <v>68807</v>
+        <v>83802</v>
       </c>
       <c r="D17" t="n">
-        <v>-18241.03</v>
+        <v>-1915.9</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="G17" t="n">
-        <v>110.62</v>
+        <v>279.99</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K17" t="n">
+        <v>834</v>
+      </c>
+      <c r="L17" t="n">
+        <v>103</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.198</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:01.123</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1780022220137</v>
+      </c>
+      <c r="C18" t="n">
+        <v>83357</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-2265.1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>85</v>
+      </c>
+      <c r="F18" t="n">
+        <v>679</v>
+      </c>
+      <c r="G18" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K18" t="n">
+        <v>984</v>
+      </c>
+      <c r="L18" t="n">
+        <v>140</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.533</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:01.125</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1780022220337</v>
+      </c>
+      <c r="C19" t="n">
+        <v>81797</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-3711.85</v>
+      </c>
+      <c r="E19" t="n">
+        <v>85</v>
+      </c>
+      <c r="F19" t="n">
+        <v>679</v>
+      </c>
+      <c r="G19" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>786</v>
+      </c>
+      <c r="L19" t="n">
+        <v>101</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:01.371</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1780022220537</v>
+      </c>
+      <c r="C20" t="n">
+        <v>81793</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-3530.25</v>
+      </c>
+      <c r="E20" t="n">
+        <v>85</v>
+      </c>
+      <c r="F20" t="n">
+        <v>679</v>
+      </c>
+      <c r="G20" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K20" t="n">
+        <v>833</v>
+      </c>
+      <c r="L20" t="n">
+        <v>111</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.169</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:03.719</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1780022220737</v>
+      </c>
+      <c r="C21" t="n">
+        <v>81954</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-3192.74</v>
+      </c>
+      <c r="E21" t="n">
+        <v>85</v>
+      </c>
+      <c r="F21" t="n">
+        <v>679</v>
+      </c>
+      <c r="G21" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2981</v>
+      </c>
+      <c r="L21" t="n">
+        <v>108</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.913</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:03.755</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1780022220937</v>
+      </c>
+      <c r="C22" t="n">
+        <v>82535</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-2452.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>85</v>
+      </c>
+      <c r="F22" t="n">
+        <v>679</v>
+      </c>
+      <c r="G22" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2816</v>
+      </c>
+      <c r="L22" t="n">
+        <v>122</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.245</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.001</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1780022221137</v>
+      </c>
+      <c r="C23" t="n">
+        <v>83345</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1519.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>85</v>
+      </c>
+      <c r="F23" t="n">
+        <v>679</v>
+      </c>
+      <c r="G23" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2863</v>
+      </c>
+      <c r="L23" t="n">
+        <v>107</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.094</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.009</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1780022221356</v>
+      </c>
+      <c r="C24" t="n">
+        <v>83500</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-1288.52</v>
+      </c>
+      <c r="E24" t="n">
+        <v>85</v>
+      </c>
+      <c r="F24" t="n">
+        <v>679</v>
+      </c>
+      <c r="G24" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2652</v>
+      </c>
+      <c r="L24" t="n">
+        <v>104</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.063</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1780022221556</v>
+      </c>
+      <c r="C25" t="n">
+        <v>83329</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1395.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>85</v>
+      </c>
+      <c r="F25" t="n">
+        <v>679</v>
+      </c>
+      <c r="G25" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2505</v>
+      </c>
+      <c r="L25" t="n">
+        <v>102</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.093</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1780022221756</v>
+      </c>
+      <c r="C26" t="n">
+        <v>82937</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1717.34</v>
+      </c>
+      <c r="E26" t="n">
+        <v>85</v>
+      </c>
+      <c r="F26" t="n">
+        <v>679</v>
+      </c>
+      <c r="G26" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2336</v>
+      </c>
+      <c r="L26" t="n">
+        <v>103</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.336</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.095</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1780022221956</v>
+      </c>
+      <c r="C27" t="n">
+        <v>83038</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-1530.48</v>
+      </c>
+      <c r="E27" t="n">
+        <v>85</v>
+      </c>
+      <c r="F27" t="n">
+        <v>679</v>
+      </c>
+      <c r="G27" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2138</v>
+      </c>
+      <c r="L27" t="n">
+        <v>104</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.055</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.097</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1780022222156</v>
+      </c>
+      <c r="C28" t="n">
+        <v>83868</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-623.95</v>
+      </c>
+      <c r="E28" t="n">
+        <v>85</v>
+      </c>
+      <c r="F28" t="n">
+        <v>679</v>
+      </c>
+      <c r="G28" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J28" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1940</v>
+      </c>
+      <c r="L28" t="n">
+        <v>110</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.628</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.098</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1780022222356</v>
+      </c>
+      <c r="C29" t="n">
+        <v>83902</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-558.75</v>
+      </c>
+      <c r="E29" t="n">
+        <v>85</v>
+      </c>
+      <c r="F29" t="n">
+        <v>679</v>
+      </c>
+      <c r="G29" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J29" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1741</v>
+      </c>
+      <c r="L29" t="n">
+        <v>108</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.805</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.100</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1780022222556</v>
+      </c>
+      <c r="C30" t="n">
+        <v>84502</v>
+      </c>
+      <c r="D30" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="E30" t="n">
+        <v>85</v>
+      </c>
+      <c r="F30" t="n">
+        <v>679</v>
+      </c>
+      <c r="G30" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J30" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1543</v>
+      </c>
+      <c r="L30" t="n">
+        <v>109</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.247</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1780022222796</v>
+      </c>
+      <c r="C31" t="n">
+        <v>84566</v>
+      </c>
+      <c r="D31" t="n">
+        <v>129.72</v>
+      </c>
+      <c r="E31" t="n">
+        <v>85</v>
+      </c>
+      <c r="F31" t="n">
+        <v>679</v>
+      </c>
+      <c r="G31" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L31" t="n">
+        <v>108</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.249</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1780022223015</v>
+      </c>
+      <c r="C32" t="n">
+        <v>84129</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-313.76</v>
+      </c>
+      <c r="E32" t="n">
+        <v>85</v>
+      </c>
+      <c r="F32" t="n">
+        <v>679</v>
+      </c>
+      <c r="G32" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1233</v>
+      </c>
+      <c r="L32" t="n">
+        <v>113</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.961</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.273</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1780022223216</v>
+      </c>
+      <c r="C33" t="n">
+        <v>83899</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-528.0700000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>85</v>
+      </c>
+      <c r="F33" t="n">
+        <v>679</v>
+      </c>
+      <c r="G33" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J33" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1056</v>
+      </c>
+      <c r="L33" t="n">
+        <v>105</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.798</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.372</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1780022223415</v>
+      </c>
+      <c r="C34" t="n">
+        <v>82976</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-1424.67</v>
+      </c>
+      <c r="E34" t="n">
+        <v>85</v>
+      </c>
+      <c r="F34" t="n">
+        <v>679</v>
+      </c>
+      <c r="G34" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K34" t="n">
+        <v>956</v>
+      </c>
+      <c r="L34" t="n">
+        <v>109</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.726</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.391</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1780022223615</v>
+      </c>
+      <c r="C35" t="n">
+        <v>83218</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-1111.44</v>
+      </c>
+      <c r="E35" t="n">
+        <v>85</v>
+      </c>
+      <c r="F35" t="n">
+        <v>679</v>
+      </c>
+      <c r="G35" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>775</v>
+      </c>
+      <c r="L35" t="n">
+        <v>99</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.756</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1780022223815</v>
+      </c>
+      <c r="C36" t="n">
+        <v>82723</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-1550.87</v>
+      </c>
+      <c r="E36" t="n">
+        <v>85</v>
+      </c>
+      <c r="F36" t="n">
+        <v>679</v>
+      </c>
+      <c r="G36" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K36" t="n">
+        <v>939</v>
+      </c>
+      <c r="L36" t="n">
+        <v>110</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.483</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:04.758</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1780022224015</v>
+      </c>
+      <c r="C37" t="n">
+        <v>83375</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-821.3200000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>85</v>
+      </c>
+      <c r="F37" t="n">
+        <v>679</v>
+      </c>
+      <c r="G37" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>741</v>
+      </c>
+      <c r="L37" t="n">
+        <v>104</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.274</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:05.303</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1780022224215</v>
+      </c>
+      <c r="C38" t="n">
+        <v>83600</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-555.26</v>
+      </c>
+      <c r="E38" t="n">
+        <v>85</v>
+      </c>
+      <c r="F38" t="n">
+        <v>679</v>
+      </c>
+      <c r="G38" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1087</v>
+      </c>
+      <c r="L38" t="n">
+        <v>106</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.326</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:05.352</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1780022224415</v>
+      </c>
+      <c r="C39" t="n">
+        <v>82513</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-1614.49</v>
+      </c>
+      <c r="E39" t="n">
+        <v>85</v>
+      </c>
+      <c r="F39" t="n">
+        <v>679</v>
+      </c>
+      <c r="G39" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>935</v>
+      </c>
+      <c r="L39" t="n">
+        <v>105</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:05.624</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1780022224615</v>
+      </c>
+      <c r="C40" t="n">
+        <v>81827</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-2219.77</v>
+      </c>
+      <c r="E40" t="n">
+        <v>85</v>
+      </c>
+      <c r="F40" t="n">
+        <v>679</v>
+      </c>
+      <c r="G40" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L40" t="n">
+        <v>112</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.221</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:05.625</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1780022224834</v>
+      </c>
+      <c r="C41" t="n">
+        <v>82180</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-1755.78</v>
+      </c>
+      <c r="E41" t="n">
+        <v>85</v>
+      </c>
+      <c r="F41" t="n">
+        <v>679</v>
+      </c>
+      <c r="G41" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>790</v>
+      </c>
+      <c r="L41" t="n">
+        <v>107</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.259</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:05.957</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1780022225034</v>
+      </c>
+      <c r="C42" t="n">
+        <v>82291</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-1556.99</v>
+      </c>
+      <c r="E42" t="n">
+        <v>85</v>
+      </c>
+      <c r="F42" t="n">
+        <v>679</v>
+      </c>
+      <c r="G42" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K42" t="n">
+        <v>922</v>
+      </c>
+      <c r="L42" t="n">
+        <v>114</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.755</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:05.959</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1780022225234</v>
+      </c>
+      <c r="C43" t="n">
+        <v>83501</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-269.14</v>
+      </c>
+      <c r="E43" t="n">
+        <v>85</v>
+      </c>
+      <c r="F43" t="n">
+        <v>679</v>
+      </c>
+      <c r="G43" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>723</v>
+      </c>
+      <c r="L43" t="n">
+        <v>104</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.209</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:06.394</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1780022225434</v>
+      </c>
+      <c r="C44" t="n">
+        <v>83919</v>
+      </c>
+      <c r="D44" t="n">
+        <v>162.32</v>
+      </c>
+      <c r="E44" t="n">
+        <v>85</v>
+      </c>
+      <c r="F44" t="n">
+        <v>679</v>
+      </c>
+      <c r="G44" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K44" t="n">
+        <v>960</v>
+      </c>
+      <c r="L44" t="n">
+        <v>113</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:06.395</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1780022225634</v>
+      </c>
+      <c r="C45" t="n">
+        <v>82824</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-940.8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>85</v>
+      </c>
+      <c r="F45" t="n">
+        <v>679</v>
+      </c>
+      <c r="G45" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>761</v>
+      </c>
+      <c r="L45" t="n">
+        <v>107</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.605</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:06.992</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1780022225834</v>
+      </c>
+      <c r="C46" t="n">
+        <v>82829</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-888.76</v>
+      </c>
+      <c r="E46" t="n">
+        <v>85</v>
+      </c>
+      <c r="F46" t="n">
+        <v>679</v>
+      </c>
+      <c r="G46" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L46" t="n">
+        <v>115</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.059</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:07.045</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1780022226034</v>
+      </c>
+      <c r="C47" t="n">
+        <v>82409</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-1264.32</v>
+      </c>
+      <c r="E47" t="n">
+        <v>85</v>
+      </c>
+      <c r="F47" t="n">
+        <v>679</v>
+      </c>
+      <c r="G47" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L47" t="n">
+        <v>106</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.028</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:07.704</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1780022226234</v>
+      </c>
+      <c r="C48" t="n">
+        <v>82001</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-1609.11</v>
+      </c>
+      <c r="E48" t="n">
+        <v>85</v>
+      </c>
+      <c r="F48" t="n">
+        <v>679</v>
+      </c>
+      <c r="G48" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1468</v>
+      </c>
+      <c r="L48" t="n">
+        <v>110</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.704</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:07.706</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1780022226453</v>
+      </c>
+      <c r="C49" t="n">
+        <v>82553</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-976.65</v>
+      </c>
+      <c r="E49" t="n">
+        <v>85</v>
+      </c>
+      <c r="F49" t="n">
+        <v>679</v>
+      </c>
+      <c r="G49" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1251</v>
+      </c>
+      <c r="L49" t="n">
+        <v>106</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.696</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:07.721</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1780022226653</v>
+      </c>
+      <c r="C50" t="n">
+        <v>82505</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-975.8200000000001</v>
+      </c>
+      <c r="E50" t="n">
+        <v>85</v>
+      </c>
+      <c r="F50" t="n">
+        <v>679</v>
+      </c>
+      <c r="G50" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1067</v>
+      </c>
+      <c r="L50" t="n">
+        <v>105</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.062</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:09.144</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1780022226853</v>
+      </c>
+      <c r="C51" t="n">
+        <v>82980</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-452.03</v>
+      </c>
+      <c r="E51" t="n">
+        <v>85</v>
+      </c>
+      <c r="F51" t="n">
+        <v>679</v>
+      </c>
+      <c r="G51" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2290</v>
+      </c>
+      <c r="L51" t="n">
+        <v>109</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.015</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:09.145</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1780022227053</v>
+      </c>
+      <c r="C52" t="n">
+        <v>83957</v>
+      </c>
+      <c r="D52" t="n">
+        <v>547.5700000000001</v>
+      </c>
+      <c r="E52" t="n">
+        <v>85</v>
+      </c>
+      <c r="F52" t="n">
+        <v>679</v>
+      </c>
+      <c r="G52" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2091</v>
+      </c>
+      <c r="L52" t="n">
+        <v>106</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.021</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:09.161</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1780022227253</v>
+      </c>
+      <c r="C53" t="n">
+        <v>84314</v>
+      </c>
+      <c r="D53" t="n">
+        <v>877.2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>85</v>
+      </c>
+      <c r="F53" t="n">
+        <v>679</v>
+      </c>
+      <c r="G53" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1907</v>
+      </c>
+      <c r="L53" t="n">
+        <v>105</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.185</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:09.432</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1780022227453</v>
+      </c>
+      <c r="C54" t="n">
+        <v>83382</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-98.66</v>
+      </c>
+      <c r="E54" t="n">
+        <v>85</v>
+      </c>
+      <c r="F54" t="n">
+        <v>679</v>
+      </c>
+      <c r="G54" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1978</v>
+      </c>
+      <c r="L54" t="n">
+        <v>108</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.904</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:09.433</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1780022227653</v>
+      </c>
+      <c r="C55" t="n">
+        <v>82504</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-971.73</v>
+      </c>
+      <c r="E55" t="n">
+        <v>85</v>
+      </c>
+      <c r="F55" t="n">
+        <v>679</v>
+      </c>
+      <c r="G55" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1779</v>
+      </c>
+      <c r="L55" t="n">
+        <v>110</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.482</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:09.441</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1780022227853</v>
+      </c>
+      <c r="C56" t="n">
+        <v>82732</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-695.14</v>
+      </c>
+      <c r="E56" t="n">
+        <v>85</v>
+      </c>
+      <c r="F56" t="n">
+        <v>679</v>
+      </c>
+      <c r="G56" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1587</v>
+      </c>
+      <c r="L56" t="n">
+        <v>109</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.106</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:09.442</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1780022228072</v>
+      </c>
+      <c r="C57" t="n">
+        <v>82496</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-896.39</v>
+      </c>
+      <c r="E57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F57" t="n">
+        <v>679</v>
+      </c>
+      <c r="G57" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1369</v>
+      </c>
+      <c r="L57" t="n">
+        <v>105</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.744</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:09.765</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1780022228272</v>
+      </c>
+      <c r="C58" t="n">
+        <v>81778</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-1569.57</v>
+      </c>
+      <c r="E58" t="n">
+        <v>85</v>
+      </c>
+      <c r="F58" t="n">
+        <v>679</v>
+      </c>
+      <c r="G58" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1492</v>
+      </c>
+      <c r="L58" t="n">
+        <v>104</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.282</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:09.788</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1780022228472</v>
+      </c>
+      <c r="C59" t="n">
+        <v>81875</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-1394.09</v>
+      </c>
+      <c r="E59" t="n">
+        <v>85</v>
+      </c>
+      <c r="F59" t="n">
+        <v>679</v>
+      </c>
+      <c r="G59" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J59" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1314</v>
+      </c>
+      <c r="L59" t="n">
+        <v>112</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.968</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:10.117</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1780022228672</v>
+      </c>
+      <c r="C60" t="n">
+        <v>82477</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-722.39</v>
+      </c>
+      <c r="E60" t="n">
+        <v>85</v>
+      </c>
+      <c r="F60" t="n">
+        <v>679</v>
+      </c>
+      <c r="G60" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J60" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1444</v>
+      </c>
+      <c r="L60" t="n">
+        <v>108</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.832</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:10.118</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1780022228872</v>
+      </c>
+      <c r="C61" t="n">
+        <v>82512</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-651.27</v>
+      </c>
+      <c r="E61" t="n">
+        <v>85</v>
+      </c>
+      <c r="F61" t="n">
+        <v>679</v>
+      </c>
+      <c r="G61" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L61" t="n">
+        <v>111</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:10.119</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1780022229072</v>
+      </c>
+      <c r="C62" t="n">
+        <v>83086</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-44.7</v>
+      </c>
+      <c r="E62" t="n">
+        <v>85</v>
+      </c>
+      <c r="F62" t="n">
+        <v>679</v>
+      </c>
+      <c r="G62" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1046</v>
+      </c>
+      <c r="L62" t="n">
+        <v>104</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.859</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:10.120</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1780022229272</v>
+      </c>
+      <c r="C63" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D63" t="n">
+        <v>871.53</v>
+      </c>
+      <c r="E63" t="n">
+        <v>85</v>
+      </c>
+      <c r="F63" t="n">
+        <v>679</v>
+      </c>
+      <c r="G63" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K63" t="n">
+        <v>847</v>
+      </c>
+      <c r="L63" t="n">
+        <v>106</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.864</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:10.866</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1780022229472</v>
+      </c>
+      <c r="C64" t="n">
+        <v>83313</v>
+      </c>
+      <c r="D64" t="n">
+        <v>140.96</v>
+      </c>
+      <c r="E64" t="n">
+        <v>85</v>
+      </c>
+      <c r="F64" t="n">
+        <v>679</v>
+      </c>
+      <c r="G64" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1393</v>
+      </c>
+      <c r="L64" t="n">
+        <v>111</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.587</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:10.878</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1780022229672</v>
+      </c>
+      <c r="C65" t="n">
+        <v>82686</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-493.09</v>
+      </c>
+      <c r="E65" t="n">
+        <v>85</v>
+      </c>
+      <c r="F65" t="n">
+        <v>679</v>
+      </c>
+      <c r="G65" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1205</v>
+      </c>
+      <c r="L65" t="n">
+        <v>106</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.103</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:11.201</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1780022229891</v>
+      </c>
+      <c r="C66" t="n">
+        <v>82982</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-172.44</v>
+      </c>
+      <c r="E66" t="n">
+        <v>85</v>
+      </c>
+      <c r="F66" t="n">
+        <v>679</v>
+      </c>
+      <c r="G66" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1309</v>
+      </c>
+      <c r="L66" t="n">
+        <v>111</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:11.202</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1780022230091</v>
+      </c>
+      <c r="C67" t="n">
+        <v>83847</v>
+      </c>
+      <c r="D67" t="n">
+        <v>701.1799999999999</v>
+      </c>
+      <c r="E67" t="n">
+        <v>85</v>
+      </c>
+      <c r="F67" t="n">
+        <v>679</v>
+      </c>
+      <c r="G67" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1110</v>
+      </c>
+      <c r="L67" t="n">
+        <v>105</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.012</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:11.203</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1780022230291</v>
+      </c>
+      <c r="C68" t="n">
+        <v>83699</v>
+      </c>
+      <c r="D68" t="n">
+        <v>518.13</v>
+      </c>
+      <c r="E68" t="n">
+        <v>85</v>
+      </c>
+      <c r="F68" t="n">
+        <v>679</v>
+      </c>
+      <c r="G68" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>911</v>
+      </c>
+      <c r="L68" t="n">
+        <v>105</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.053</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.786</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1780022230491</v>
+      </c>
+      <c r="C69" t="n">
+        <v>84134</v>
+      </c>
+      <c r="D69" t="n">
+        <v>927.22</v>
+      </c>
+      <c r="E69" t="n">
+        <v>85</v>
+      </c>
+      <c r="F69" t="n">
+        <v>679</v>
+      </c>
+      <c r="G69" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3293</v>
+      </c>
+      <c r="L69" t="n">
+        <v>109</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.452</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.787</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1780022230691</v>
+      </c>
+      <c r="C70" t="n">
+        <v>83998</v>
+      </c>
+      <c r="D70" t="n">
+        <v>744.86</v>
+      </c>
+      <c r="E70" t="n">
+        <v>85</v>
+      </c>
+      <c r="F70" t="n">
+        <v>679</v>
+      </c>
+      <c r="G70" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>3095</v>
+      </c>
+      <c r="L70" t="n">
+        <v>107</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.161</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.797</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1780022230891</v>
+      </c>
+      <c r="C71" t="n">
+        <v>83665</v>
+      </c>
+      <c r="D71" t="n">
+        <v>374.62</v>
+      </c>
+      <c r="E71" t="n">
+        <v>85</v>
+      </c>
+      <c r="F71" t="n">
+        <v>679</v>
+      </c>
+      <c r="G71" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2904</v>
+      </c>
+      <c r="L71" t="n">
+        <v>109</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.227</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.812</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1780022231091</v>
+      </c>
+      <c r="C72" t="n">
+        <v>83261</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-48.12</v>
+      </c>
+      <c r="E72" t="n">
+        <v>85</v>
+      </c>
+      <c r="F72" t="n">
+        <v>679</v>
+      </c>
+      <c r="G72" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2720</v>
+      </c>
+      <c r="L72" t="n">
+        <v>107</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.229</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.842</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1780022231291</v>
+      </c>
+      <c r="C73" t="n">
+        <v>83375</v>
+      </c>
+      <c r="D73" t="n">
+        <v>68.29000000000001</v>
+      </c>
+      <c r="E73" t="n">
+        <v>85</v>
+      </c>
+      <c r="F73" t="n">
+        <v>679</v>
+      </c>
+      <c r="G73" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2551</v>
+      </c>
+      <c r="L73" t="n">
+        <v>104</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.882</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1780022231491</v>
+      </c>
+      <c r="C74" t="n">
+        <v>80399</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-2911.12</v>
+      </c>
+      <c r="E74" t="n">
+        <v>85</v>
+      </c>
+      <c r="F74" t="n">
+        <v>679</v>
+      </c>
+      <c r="G74" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2390</v>
+      </c>
+      <c r="L74" t="n">
+        <v>104</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.138</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.953</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1780022231710</v>
+      </c>
+      <c r="C75" t="n">
+        <v>78375</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-4789.57</v>
+      </c>
+      <c r="E75" t="n">
+        <v>85</v>
+      </c>
+      <c r="F75" t="n">
+        <v>679</v>
+      </c>
+      <c r="G75" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2242</v>
+      </c>
+      <c r="L75" t="n">
+        <v>108</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.313</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.975</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1780022231910</v>
+      </c>
+      <c r="C76" t="n">
+        <v>79621</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-3304.09</v>
+      </c>
+      <c r="E76" t="n">
+        <v>85</v>
+      </c>
+      <c r="F76" t="n">
+        <v>679</v>
+      </c>
+      <c r="G76" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2064</v>
+      </c>
+      <c r="L76" t="n">
+        <v>109</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.272</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.977</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1780022232110</v>
+      </c>
+      <c r="C77" t="n">
+        <v>83400</v>
+      </c>
+      <c r="D77" t="n">
+        <v>640.11</v>
+      </c>
+      <c r="E77" t="n">
+        <v>85</v>
+      </c>
+      <c r="F77" t="n">
+        <v>679</v>
+      </c>
+      <c r="G77" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J77" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1866</v>
+      </c>
+      <c r="L77" t="n">
+        <v>108</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.209</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.979</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1780022232310</v>
+      </c>
+      <c r="C78" t="n">
+        <v>86008</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3216.11</v>
+      </c>
+      <c r="E78" t="n">
+        <v>85</v>
+      </c>
+      <c r="F78" t="n">
+        <v>679</v>
+      </c>
+      <c r="G78" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1667</v>
+      </c>
+      <c r="L78" t="n">
+        <v>112</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.980</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1780022232510</v>
+      </c>
+      <c r="C79" t="n">
+        <v>87644</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4691.3</v>
+      </c>
+      <c r="E79" t="n">
+        <v>85</v>
+      </c>
+      <c r="F79" t="n">
+        <v>679</v>
+      </c>
+      <c r="G79" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1469</v>
+      </c>
+      <c r="L79" t="n">
+        <v>104</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.066</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:13.982</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1780022232710</v>
+      </c>
+      <c r="C80" t="n">
+        <v>87063</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3875.74</v>
+      </c>
+      <c r="E80" t="n">
+        <v>85</v>
+      </c>
+      <c r="F80" t="n">
+        <v>679</v>
+      </c>
+      <c r="G80" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1270</v>
+      </c>
+      <c r="L80" t="n">
+        <v>105</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.193</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:14.202</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1780022232910</v>
+      </c>
+      <c r="C81" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4207.95</v>
+      </c>
+      <c r="E81" t="n">
+        <v>85</v>
+      </c>
+      <c r="F81" t="n">
+        <v>679</v>
+      </c>
+      <c r="G81" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1291</v>
+      </c>
+      <c r="L81" t="n">
+        <v>114</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.093</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:14.215</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1780022233110</v>
+      </c>
+      <c r="C82" t="n">
+        <v>88170</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4578.55</v>
+      </c>
+      <c r="E82" t="n">
+        <v>85</v>
+      </c>
+      <c r="F82" t="n">
+        <v>679</v>
+      </c>
+      <c r="G82" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1105</v>
+      </c>
+      <c r="L82" t="n">
+        <v>106</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:14.234</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1780022233329</v>
+      </c>
+      <c r="C83" t="n">
+        <v>87976</v>
+      </c>
+      <c r="D83" t="n">
+        <v>4155.63</v>
+      </c>
+      <c r="E83" t="n">
+        <v>85</v>
+      </c>
+      <c r="F83" t="n">
+        <v>679</v>
+      </c>
+      <c r="G83" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>904</v>
+      </c>
+      <c r="L83" t="n">
+        <v>107</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.231</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:14.694</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1780022233529</v>
+      </c>
+      <c r="C84" t="n">
+        <v>88227</v>
+      </c>
+      <c r="D84" t="n">
+        <v>4198.84</v>
+      </c>
+      <c r="E84" t="n">
+        <v>85</v>
+      </c>
+      <c r="F84" t="n">
+        <v>679</v>
+      </c>
+      <c r="G84" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1164</v>
+      </c>
+      <c r="L84" t="n">
+        <v>114</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.636</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:14.695</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1780022233729</v>
+      </c>
+      <c r="C85" t="n">
+        <v>88434</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4195.9</v>
+      </c>
+      <c r="E85" t="n">
+        <v>85</v>
+      </c>
+      <c r="F85" t="n">
+        <v>679</v>
+      </c>
+      <c r="G85" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K85" t="n">
+        <v>965</v>
+      </c>
+      <c r="L85" t="n">
+        <v>110</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.619</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:15.043</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1780022233929</v>
+      </c>
+      <c r="C86" t="n">
+        <v>87985</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3537.11</v>
+      </c>
+      <c r="E86" t="n">
+        <v>85</v>
+      </c>
+      <c r="F86" t="n">
+        <v>679</v>
+      </c>
+      <c r="G86" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1113</v>
+      </c>
+      <c r="L86" t="n">
+        <v>111</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.949</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:15.046</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1780022234129</v>
+      </c>
+      <c r="C87" t="n">
+        <v>87909</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3284.25</v>
+      </c>
+      <c r="E87" t="n">
+        <v>85</v>
+      </c>
+      <c r="F87" t="n">
+        <v>679</v>
+      </c>
+      <c r="G87" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>915</v>
+      </c>
+      <c r="L87" t="n">
+        <v>105</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.525</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:15.469</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1780022234329</v>
+      </c>
+      <c r="C88" t="n">
+        <v>88238</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3449.04</v>
+      </c>
+      <c r="E88" t="n">
+        <v>85</v>
+      </c>
+      <c r="F88" t="n">
+        <v>679</v>
+      </c>
+      <c r="G88" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1139</v>
+      </c>
+      <c r="L88" t="n">
+        <v>110</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:15.507</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1780022234529</v>
+      </c>
+      <c r="C89" t="n">
+        <v>89068</v>
+      </c>
+      <c r="D89" t="n">
+        <v>4106.59</v>
+      </c>
+      <c r="E89" t="n">
+        <v>85</v>
+      </c>
+      <c r="F89" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G89" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>977</v>
+      </c>
+      <c r="L89" t="n">
+        <v>117</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.524</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:15.827</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1780022234729</v>
+      </c>
+      <c r="C90" t="n">
+        <v>88845</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3678.26</v>
+      </c>
+      <c r="E90" t="n">
+        <v>85</v>
+      </c>
+      <c r="F90" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G90" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1097</v>
+      </c>
+      <c r="L90" t="n">
+        <v>123</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.357</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:15.828</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1780022234929</v>
+      </c>
+      <c r="C91" t="n">
+        <v>87764</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2413.35</v>
+      </c>
+      <c r="E91" t="n">
+        <v>85</v>
+      </c>
+      <c r="F91" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G91" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>899</v>
+      </c>
+      <c r="L91" t="n">
+        <v>119</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.694</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:16.244</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1780022235148</v>
+      </c>
+      <c r="C92" t="n">
+        <v>87040</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1568.68</v>
+      </c>
+      <c r="E92" t="n">
+        <v>85</v>
+      </c>
+      <c r="F92" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G92" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1094</v>
+      </c>
+      <c r="L92" t="n">
+        <v>112</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.255</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:16.245</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1780022235348</v>
+      </c>
+      <c r="C93" t="n">
+        <v>86185</v>
+      </c>
+      <c r="D93" t="n">
+        <v>635.24</v>
+      </c>
+      <c r="E93" t="n">
+        <v>85</v>
+      </c>
+      <c r="F93" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G93" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>896</v>
+      </c>
+      <c r="L93" t="n">
+        <v>115</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.613</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:16.635</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1780022235548</v>
+      </c>
+      <c r="C94" t="n">
+        <v>85786</v>
+      </c>
+      <c r="D94" t="n">
+        <v>204.48</v>
+      </c>
+      <c r="E94" t="n">
+        <v>85</v>
+      </c>
+      <c r="F94" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G94" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1086</v>
+      </c>
+      <c r="L94" t="n">
+        <v>119</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.883</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:16.645</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1780022235748</v>
+      </c>
+      <c r="C95" t="n">
+        <v>85635</v>
+      </c>
+      <c r="D95" t="n">
+        <v>43.26</v>
+      </c>
+      <c r="E95" t="n">
+        <v>85</v>
+      </c>
+      <c r="F95" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G95" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>896</v>
+      </c>
+      <c r="L95" t="n">
+        <v>120</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.049</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:17.075</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1780022235948</v>
+      </c>
+      <c r="C96" t="n">
+        <v>85649</v>
+      </c>
+      <c r="D96" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="E96" t="n">
+        <v>85</v>
+      </c>
+      <c r="F96" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G96" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L96" t="n">
+        <v>116</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2.129</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:17.077</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1780022236148</v>
+      </c>
+      <c r="C97" t="n">
+        <v>85656</v>
+      </c>
+      <c r="D97" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="E97" t="n">
+        <v>85</v>
+      </c>
+      <c r="F97" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G97" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>928</v>
+      </c>
+      <c r="L97" t="n">
+        <v>121</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.346</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:17.461</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1780022236348</v>
+      </c>
+      <c r="C98" t="n">
+        <v>85647</v>
+      </c>
+      <c r="D98" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="E98" t="n">
+        <v>85</v>
+      </c>
+      <c r="F98" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G98" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1112</v>
+      </c>
+      <c r="L98" t="n">
+        <v>121</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.104</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:17.463</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1780022236548</v>
+      </c>
+      <c r="C99" t="n">
+        <v>85717</v>
+      </c>
+      <c r="D99" t="n">
+        <v>115</v>
+      </c>
+      <c r="E99" t="n">
+        <v>85</v>
+      </c>
+      <c r="F99" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G99" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>914</v>
+      </c>
+      <c r="L99" t="n">
+        <v>122</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.043</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:18.528</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1780022236749</v>
+      </c>
+      <c r="C100" t="n">
+        <v>85676</v>
+      </c>
+      <c r="D100" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="E100" t="n">
+        <v>85</v>
+      </c>
+      <c r="F100" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G100" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1777</v>
+      </c>
+      <c r="L100" t="n">
+        <v>110</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2.041</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:18.543</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1780022236967</v>
+      </c>
+      <c r="C101" t="n">
+        <v>85383</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-228.16</v>
+      </c>
+      <c r="E101" t="n">
+        <v>85</v>
+      </c>
+      <c r="F101" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G101" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1575</v>
+      </c>
+      <c r="L101" t="n">
+        <v>124</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.953</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:18.550</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1780022237167</v>
+      </c>
+      <c r="C102" t="n">
+        <v>84827</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-772.75</v>
+      </c>
+      <c r="E102" t="n">
+        <v>85</v>
+      </c>
+      <c r="F102" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G102" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1381</v>
+      </c>
+      <c r="L102" t="n">
+        <v>117</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.438</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:18.552</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1780022237367</v>
+      </c>
+      <c r="C103" t="n">
+        <v>84276</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-1285.11</v>
+      </c>
+      <c r="E103" t="n">
+        <v>85</v>
+      </c>
+      <c r="F103" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G103" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1183</v>
+      </c>
+      <c r="L103" t="n">
+        <v>124</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.907</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:18.761</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1780022237568</v>
+      </c>
+      <c r="C104" t="n">
+        <v>84002</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-1494.86</v>
+      </c>
+      <c r="E104" t="n">
+        <v>85</v>
+      </c>
+      <c r="F104" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G104" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1191</v>
+      </c>
+      <c r="L104" t="n">
+        <v>111</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.392</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:18.807</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1780022237767</v>
+      </c>
+      <c r="C105" t="n">
+        <v>83987</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-1435.11</v>
+      </c>
+      <c r="E105" t="n">
+        <v>85</v>
+      </c>
+      <c r="F105" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G105" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1038</v>
+      </c>
+      <c r="L105" t="n">
+        <v>122</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.384</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:19.172</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1780022237968</v>
+      </c>
+      <c r="C106" t="n">
+        <v>83823</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-1527.36</v>
+      </c>
+      <c r="E106" t="n">
+        <v>85</v>
+      </c>
+      <c r="F106" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G106" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1203</v>
+      </c>
+      <c r="L106" t="n">
+        <v>138</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:19.173</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1780022238167</v>
+      </c>
+      <c r="C107" t="n">
+        <v>83566</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-1707.99</v>
+      </c>
+      <c r="E107" t="n">
+        <v>85</v>
+      </c>
+      <c r="F107" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G107" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1006</v>
+      </c>
+      <c r="L107" t="n">
+        <v>116</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.704</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:19.175</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1780022238367</v>
+      </c>
+      <c r="C108" t="n">
+        <v>83617</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-1571.59</v>
+      </c>
+      <c r="E108" t="n">
+        <v>85</v>
+      </c>
+      <c r="F108" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G108" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K108" t="n">
+        <v>807</v>
+      </c>
+      <c r="L108" t="n">
+        <v>110</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:19.541</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1780022238567</v>
+      </c>
+      <c r="C109" t="n">
+        <v>83481</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-1629.01</v>
+      </c>
+      <c r="E109" t="n">
+        <v>85</v>
+      </c>
+      <c r="F109" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G109" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K109" t="n">
+        <v>973</v>
+      </c>
+      <c r="L109" t="n">
+        <v>119</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.495</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:19.543</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1780022238767</v>
+      </c>
+      <c r="C110" t="n">
+        <v>83562</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-1466.56</v>
+      </c>
+      <c r="E110" t="n">
+        <v>85</v>
+      </c>
+      <c r="F110" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G110" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K110" t="n">
+        <v>775</v>
+      </c>
+      <c r="L110" t="n">
+        <v>114</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.279</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:20.217</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1780022238986</v>
+      </c>
+      <c r="C111" t="n">
+        <v>83563</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-1392.23</v>
+      </c>
+      <c r="E111" t="n">
+        <v>85</v>
+      </c>
+      <c r="F111" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G111" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L111" t="n">
+        <v>111</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1.643</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:20.218</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1780022239186</v>
+      </c>
+      <c r="C112" t="n">
+        <v>83463</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-1422.62</v>
+      </c>
+      <c r="E112" t="n">
+        <v>85</v>
+      </c>
+      <c r="F112" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G112" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L112" t="n">
+        <v>112</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.724</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:20.259</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1780022239386</v>
+      </c>
+      <c r="C113" t="n">
+        <v>83627</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-1187.49</v>
+      </c>
+      <c r="E113" t="n">
+        <v>85</v>
+      </c>
+      <c r="F113" t="n">
+        <v>17910</v>
+      </c>
+      <c r="G113" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K113" t="n">
+        <v>871</v>
+      </c>
+      <c r="L113" t="n">
+        <v>101</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.277</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:20.621</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1780022239586</v>
+      </c>
+      <c r="C114" t="n">
+        <v>84435</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-320.12</v>
+      </c>
+      <c r="E114" t="n">
+        <v>85</v>
+      </c>
+      <c r="F114" t="n">
+        <v>5077</v>
+      </c>
+      <c r="G114" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1033</v>
+      </c>
+      <c r="L114" t="n">
+        <v>114</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.902</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:20.622</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1780022239786</v>
+      </c>
+      <c r="C115" t="n">
+        <v>83925</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-814.11</v>
+      </c>
+      <c r="E115" t="n">
+        <v>85</v>
+      </c>
+      <c r="F115" t="n">
+        <v>5077</v>
+      </c>
+      <c r="G115" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K115" t="n">
+        <v>835</v>
+      </c>
+      <c r="L115" t="n">
+        <v>107</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.168</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:21.732</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1780022239986</v>
+      </c>
+      <c r="C116" t="n">
+        <v>83759</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-939.4</v>
+      </c>
+      <c r="E116" t="n">
+        <v>85</v>
+      </c>
+      <c r="F116" t="n">
+        <v>5077</v>
+      </c>
+      <c r="G116" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1744</v>
+      </c>
+      <c r="L116" t="n">
+        <v>118</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.391</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:21.733</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1780022240186</v>
+      </c>
+      <c r="C117" t="n">
+        <v>83633</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-1018.43</v>
+      </c>
+      <c r="E117" t="n">
+        <v>85</v>
+      </c>
+      <c r="F117" t="n">
+        <v>5077</v>
+      </c>
+      <c r="G117" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1546</v>
+      </c>
+      <c r="L117" t="n">
+        <v>117</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:22.281</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1780022240386</v>
+      </c>
+      <c r="C118" t="n">
+        <v>83612</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-988.51</v>
+      </c>
+      <c r="E118" t="n">
+        <v>85</v>
+      </c>
+      <c r="F118" t="n">
+        <v>5077</v>
+      </c>
+      <c r="G118" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1895</v>
+      </c>
+      <c r="L118" t="n">
+        <v>116</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.681</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:22.282</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1780022240586</v>
+      </c>
+      <c r="C119" t="n">
+        <v>83722</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-829.09</v>
+      </c>
+      <c r="E119" t="n">
+        <v>85</v>
+      </c>
+      <c r="F119" t="n">
+        <v>5077</v>
+      </c>
+      <c r="G119" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1696</v>
+      </c>
+      <c r="L119" t="n">
+        <v>111</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:22.284</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1780022240805</v>
+      </c>
+      <c r="C120" t="n">
+        <v>83983</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-526.63</v>
+      </c>
+      <c r="E120" t="n">
+        <v>68</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G120" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1478</v>
+      </c>
+      <c r="L120" t="n">
+        <v>117</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:22.286</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1780022241005</v>
+      </c>
+      <c r="C121" t="n">
+        <v>84866</v>
+      </c>
+      <c r="D121" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="E121" t="n">
+        <v>68</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G121" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1280</v>
+      </c>
+      <c r="L121" t="n">
+        <v>98</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.075</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1780022241205</v>
+      </c>
+      <c r="C122" t="n">
+        <v>84787</v>
+      </c>
+      <c r="D122" t="n">
+        <v>284.56</v>
+      </c>
+      <c r="E122" t="n">
+        <v>68</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G122" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1869</v>
+      </c>
+      <c r="L122" t="n">
+        <v>104</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.589</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.105</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1780022241405</v>
+      </c>
+      <c r="C123" t="n">
+        <v>84792</v>
+      </c>
+      <c r="D123" t="n">
+        <v>275.34</v>
+      </c>
+      <c r="E123" t="n">
+        <v>68</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G123" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1699</v>
+      </c>
+      <c r="L123" t="n">
+        <v>117</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.883</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.113</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1780022241605</v>
+      </c>
+      <c r="C124" t="n">
+        <v>84863</v>
+      </c>
+      <c r="D124" t="n">
+        <v>332.57</v>
+      </c>
+      <c r="E124" t="n">
+        <v>68</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G124" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1507</v>
+      </c>
+      <c r="L124" t="n">
+        <v>109</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.863</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.114</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1780022241805</v>
+      </c>
+      <c r="C125" t="n">
+        <v>85133</v>
+      </c>
+      <c r="D125" t="n">
+        <v>585.9400000000001</v>
+      </c>
+      <c r="E125" t="n">
+        <v>68</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G125" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1309</v>
+      </c>
+      <c r="L125" t="n">
+        <v>108</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.430</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1780022242005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>85593</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1016.64</v>
+      </c>
+      <c r="E126" t="n">
+        <v>68</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G126" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1424</v>
+      </c>
+      <c r="L126" t="n">
+        <v>115</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.434</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1780022242205</v>
+      </c>
+      <c r="C127" t="n">
+        <v>85104</v>
+      </c>
+      <c r="D127" t="n">
+        <v>476.81</v>
+      </c>
+      <c r="E127" t="n">
+        <v>68</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G127" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1228</v>
+      </c>
+      <c r="L127" t="n">
+        <v>108</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.009</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.435</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1780022242424</v>
+      </c>
+      <c r="C128" t="n">
+        <v>83873</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-778.03</v>
+      </c>
+      <c r="E128" t="n">
+        <v>68</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G128" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L128" t="n">
+        <v>111</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.436</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1780022242624</v>
+      </c>
+      <c r="C129" t="n">
+        <v>83371</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-1241.13</v>
+      </c>
+      <c r="E129" t="n">
+        <v>68</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G129" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K129" t="n">
+        <v>811</v>
+      </c>
+      <c r="L129" t="n">
+        <v>108</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.634</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.846</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1780022242824</v>
+      </c>
+      <c r="C130" t="n">
+        <v>82724</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-1826.07</v>
+      </c>
+      <c r="E130" t="n">
+        <v>68</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G130" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1021</v>
+      </c>
+      <c r="L130" t="n">
+        <v>116</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.715</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:23.848</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1780022243024</v>
+      </c>
+      <c r="C131" t="n">
+        <v>82143</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-2315.77</v>
+      </c>
+      <c r="E131" t="n">
+        <v>68</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G131" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>823</v>
+      </c>
+      <c r="L131" t="n">
+        <v>111</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.745</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:24.226</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1780022243224</v>
+      </c>
+      <c r="C132" t="n">
+        <v>81836</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-2506.98</v>
+      </c>
+      <c r="E132" t="n">
+        <v>68</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G132" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1001</v>
+      </c>
+      <c r="L132" t="n">
+        <v>116</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.773</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:24.227</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1780022243424</v>
+      </c>
+      <c r="C133" t="n">
+        <v>81861</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-2356.63</v>
+      </c>
+      <c r="E133" t="n">
+        <v>68</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G133" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K133" t="n">
+        <v>802</v>
+      </c>
+      <c r="L133" t="n">
+        <v>106</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.736</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:24.843</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1780022243624</v>
+      </c>
+      <c r="C134" t="n">
+        <v>81978</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-2121.8</v>
+      </c>
+      <c r="E134" t="n">
+        <v>68</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G134" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1218</v>
+      </c>
+      <c r="L134" t="n">
+        <v>115</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.775</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:24.857</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1780022243824</v>
+      </c>
+      <c r="C135" t="n">
+        <v>81756</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-2237.71</v>
+      </c>
+      <c r="E135" t="n">
+        <v>68</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G135" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1033</v>
+      </c>
+      <c r="L135" t="n">
+        <v>107</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.599</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:25.092</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1780022244024</v>
+      </c>
+      <c r="C136" t="n">
+        <v>83525</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-356.82</v>
+      </c>
+      <c r="E136" t="n">
+        <v>68</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G136" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1066</v>
+      </c>
+      <c r="L136" t="n">
+        <v>117</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.407</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:25.122</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1780022244243</v>
+      </c>
+      <c r="C137" t="n">
+        <v>84407</v>
+      </c>
+      <c r="D137" t="n">
+        <v>543.02</v>
+      </c>
+      <c r="E137" t="n">
+        <v>68</v>
+      </c>
+      <c r="F137" t="n">
+        <v>3299</v>
+      </c>
+      <c r="G137" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K137" t="n">
+        <v>878</v>
+      </c>
+      <c r="L137" t="n">
+        <v>115</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:25.467</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1780022244443</v>
+      </c>
+      <c r="C138" t="n">
+        <v>84420</v>
+      </c>
+      <c r="D138" t="n">
+        <v>528.87</v>
+      </c>
+      <c r="E138" t="n">
+        <v>68</v>
+      </c>
+      <c r="F138" t="n">
+        <v>3299</v>
+      </c>
+      <c r="G138" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1022</v>
+      </c>
+      <c r="L138" t="n">
+        <v>114</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.408</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:25.469</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1780022244643</v>
+      </c>
+      <c r="C139" t="n">
+        <v>83919</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E139" t="n">
+        <v>68</v>
+      </c>
+      <c r="F139" t="n">
+        <v>3299</v>
+      </c>
+      <c r="G139" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K139" t="n">
+        <v>824</v>
+      </c>
+      <c r="L139" t="n">
+        <v>106</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1.449</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:25.849</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1780022244843</v>
+      </c>
+      <c r="C140" t="n">
+        <v>83988</v>
+      </c>
+      <c r="D140" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="E140" t="n">
+        <v>68</v>
+      </c>
+      <c r="F140" t="n">
+        <v>3299</v>
+      </c>
+      <c r="G140" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1005</v>
+      </c>
+      <c r="L140" t="n">
+        <v>118</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.726</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:25.850</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1780022245043</v>
+      </c>
+      <c r="C141" t="n">
+        <v>83937</v>
+      </c>
+      <c r="D141" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="E141" t="n">
+        <v>68</v>
+      </c>
+      <c r="F141" t="n">
+        <v>3299</v>
+      </c>
+      <c r="G141" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K141" t="n">
+        <v>806</v>
+      </c>
+      <c r="L141" t="n">
+        <v>105</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:26.254</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1780022245243</v>
+      </c>
+      <c r="C142" t="n">
+        <v>84536</v>
+      </c>
+      <c r="D142" t="n">
+        <v>614.04</v>
+      </c>
+      <c r="E142" t="n">
+        <v>68</v>
+      </c>
+      <c r="F142" t="n">
+        <v>3299</v>
+      </c>
+      <c r="G142" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L142" t="n">
+        <v>116</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.624</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:26.309</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1780022245443</v>
+      </c>
+      <c r="C143" t="n">
+        <v>85203</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1250.34</v>
+      </c>
+      <c r="E143" t="n">
+        <v>62</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G143" t="n">
+        <v>312.26</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>866</v>
+      </c>
+      <c r="L143" t="n">
+        <v>111</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.749</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:26.761</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1780022245643</v>
+      </c>
+      <c r="C144" t="n">
+        <v>85787</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1771.82</v>
+      </c>
+      <c r="E144" t="n">
+        <v>62</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G144" t="n">
+        <v>312.26</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1116</v>
+      </c>
+      <c r="L144" t="n">
+        <v>115</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1.325</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:26.762</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1780022245843</v>
+      </c>
+      <c r="C145" t="n">
+        <v>86282</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2178.23</v>
+      </c>
+      <c r="E145" t="n">
+        <v>62</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G145" t="n">
+        <v>312.26</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K145" t="n">
+        <v>918</v>
+      </c>
+      <c r="L145" t="n">
+        <v>108</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1.473</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:27.106</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1780022246062</v>
+      </c>
+      <c r="C146" t="n">
+        <v>86382</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2169.32</v>
+      </c>
+      <c r="E146" t="n">
+        <v>62</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G146" t="n">
+        <v>312.26</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1043</v>
+      </c>
+      <c r="L146" t="n">
+        <v>110</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.822</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:27.107</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1780022246262</v>
+      </c>
+      <c r="C147" t="n">
+        <v>86446</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2124.85</v>
+      </c>
+      <c r="E147" t="n">
+        <v>62</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G147" t="n">
+        <v>312.26</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K147" t="n">
+        <v>844</v>
+      </c>
+      <c r="L147" t="n">
+        <v>106</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.664</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:27.527</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1780022246462</v>
+      </c>
+      <c r="C148" t="n">
+        <v>85308</v>
+      </c>
+      <c r="D148" t="n">
+        <v>880.61</v>
+      </c>
+      <c r="E148" t="n">
+        <v>62</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G148" t="n">
+        <v>312.26</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1063</v>
+      </c>
+      <c r="L148" t="n">
+        <v>117</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1.332</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:27.528</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1780022246662</v>
+      </c>
+      <c r="C149" t="n">
+        <v>85998</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1526.58</v>
+      </c>
+      <c r="E149" t="n">
+        <v>62</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G149" t="n">
+        <v>312.26</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J149" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K149" t="n">
+        <v>865</v>
+      </c>
+      <c r="L149" t="n">
+        <v>106</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.866</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:28.818</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1780022246862</v>
+      </c>
+      <c r="C150" t="n">
+        <v>86601</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2053.25</v>
+      </c>
+      <c r="E150" t="n">
+        <v>62</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G150" t="n">
+        <v>312.26</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J150" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1956</v>
+      </c>
+      <c r="L150" t="n">
+        <v>112</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
